--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_coquimbo.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_coquimbo.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.12720798617669</v>
+      </c>
+      <c r="C2">
         <v>27.0967561403877</v>
-      </c>
-      <c r="C2">
-        <v>28.12720798617669</v>
       </c>
       <c r="D2">
         <v>3.690478649248722</v>
       </c>
       <c r="E2">
-        <v>17.45655465820594</v>
+        <v>18.1204030862417</v>
       </c>
       <c r="F2">
         <v>64.42304225555235</v>
       </c>
       <c r="G2">
-        <v>18.1204030862417</v>
+        <v>17.45655465820594</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.07874553680764</v>
+      </c>
+      <c r="C3">
         <v>26.45110145786875</v>
-      </c>
-      <c r="C3">
-        <v>29.07874553680764</v>
       </c>
       <c r="D3">
         <v>3.780560902512122</v>
       </c>
       <c r="E3">
-        <v>17.00709025887111</v>
+        <v>18.696569242946</v>
       </c>
       <c r="F3">
         <v>64.29634049818289</v>
       </c>
       <c r="G3">
-        <v>18.696569242946</v>
+        <v>17.00709025887111</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>31.72881355932203</v>
+      </c>
+      <c r="C4">
         <v>33.03050847457627</v>
-      </c>
-      <c r="C4">
-        <v>31.72881355932203</v>
       </c>
       <c r="D4">
         <v>3.027504105090312</v>
       </c>
       <c r="E4">
-        <v>20.04773269689738</v>
+        <v>19.25767426549255</v>
       </c>
       <c r="F4">
         <v>60.69459303761008</v>
       </c>
       <c r="G4">
-        <v>19.25767426549255</v>
+        <v>20.04773269689738</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>40.0824896887889</v>
+      </c>
+      <c r="C5">
         <v>31.72103487064117</v>
-      </c>
-      <c r="C5">
-        <v>40.0824896887889</v>
       </c>
       <c r="D5">
         <v>3.152482269503546</v>
       </c>
       <c r="E5">
-        <v>18.46355303360977</v>
+        <v>23.33042339589699</v>
       </c>
       <c r="F5">
         <v>58.20602357049323</v>
       </c>
       <c r="G5">
-        <v>23.33042339589699</v>
+        <v>18.46355303360977</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.24967989756722</v>
+      </c>
+      <c r="C6">
         <v>31.91421254801536</v>
-      </c>
-      <c r="C6">
-        <v>30.24967989756722</v>
       </c>
       <c r="D6">
         <v>3.133400200601805</v>
       </c>
       <c r="E6">
-        <v>19.68022108172127</v>
+        <v>18.65377023292538</v>
       </c>
       <c r="F6">
         <v>61.66600868535333</v>
       </c>
       <c r="G6">
-        <v>18.65377023292538</v>
+        <v>19.68022108172127</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.14434060228453</v>
+      </c>
+      <c r="C7">
         <v>29.48598130841121</v>
-      </c>
-      <c r="C7">
-        <v>27.14434060228453</v>
       </c>
       <c r="D7">
         <v>3.391442155309033</v>
       </c>
       <c r="E7">
-        <v>18.82520635131103</v>
+        <v>17.33019524646137</v>
       </c>
       <c r="F7">
         <v>63.8445984022276</v>
       </c>
       <c r="G7">
-        <v>17.33019524646136</v>
+        <v>18.82520635131104</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.94698336828757</v>
+      </c>
+      <c r="C8">
         <v>32.88787006779496</v>
-      </c>
-      <c r="C8">
-        <v>28.94698336828757</v>
       </c>
       <c r="D8">
         <v>3.040634732314993</v>
       </c>
       <c r="E8">
-        <v>20.32187095024261</v>
+        <v>17.88674241282662</v>
       </c>
       <c r="F8">
         <v>61.79138663693078</v>
       </c>
       <c r="G8">
-        <v>17.88674241282662</v>
+        <v>20.32187095024261</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.38796276250271</v>
+      </c>
+      <c r="C9">
         <v>46.28707512448582</v>
-      </c>
-      <c r="C9">
-        <v>32.38796276250271</v>
       </c>
       <c r="D9">
         <v>2.160430308699719</v>
       </c>
       <c r="E9">
-        <v>25.9057312492427</v>
+        <v>18.12674179086393</v>
       </c>
       <c r="F9">
-        <v>55.96752695989336</v>
+        <v>55.96752695989338</v>
       </c>
       <c r="G9">
-        <v>18.12674179086393</v>
+        <v>25.90573124924271</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.61468584405753</v>
+      </c>
+      <c r="C10">
         <v>32.26894226137224</v>
-      </c>
-      <c r="C10">
-        <v>28.61468584405753</v>
       </c>
       <c r="D10">
         <v>3.098955001066325</v>
       </c>
       <c r="E10">
-        <v>20.05731884677902</v>
+        <v>17.78595260501326</v>
       </c>
       <c r="F10">
         <v>62.15672854820772</v>
       </c>
       <c r="G10">
-        <v>17.78595260501326</v>
+        <v>20.05731884677902</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>28.40733377512701</v>
+      </c>
+      <c r="C11">
         <v>30.45062955599735</v>
-      </c>
-      <c r="C11">
-        <v>28.40733377512701</v>
       </c>
       <c r="D11">
         <v>3.284004352557127</v>
       </c>
       <c r="E11">
-        <v>19.1684627685462</v>
+        <v>17.88222206771883</v>
       </c>
       <c r="F11">
         <v>62.94931516373496</v>
       </c>
       <c r="G11">
-        <v>17.88222206771883</v>
+        <v>19.1684627685462</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.43513814892826</v>
+      </c>
+      <c r="C12">
         <v>28.49158165723647</v>
-      </c>
-      <c r="C12">
-        <v>28.43513814892826</v>
       </c>
       <c r="D12">
         <v>3.509808658678006</v>
       </c>
       <c r="E12">
-        <v>18.15597859461356</v>
+        <v>18.12001052723923</v>
       </c>
       <c r="F12">
         <v>63.7240108781472</v>
       </c>
       <c r="G12">
-        <v>18.12001052723923</v>
+        <v>18.15597859461356</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.24493685966166</v>
+      </c>
+      <c r="C13">
         <v>40.6361686919228</v>
-      </c>
-      <c r="C13">
-        <v>26.24493685966166</v>
       </c>
       <c r="D13">
         <v>2.460861917326297</v>
       </c>
       <c r="E13">
-        <v>24.35037121644774</v>
+        <v>15.72672758423758</v>
       </c>
       <c r="F13">
         <v>59.92290119931467</v>
       </c>
       <c r="G13">
-        <v>15.72672758423758</v>
+        <v>24.35037121644774</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>29.15252467234087</v>
+      </c>
+      <c r="C14">
         <v>30.55715106260769</v>
-      </c>
-      <c r="C14">
-        <v>29.15252467234087</v>
       </c>
       <c r="D14">
         <v>3.272556390977444</v>
       </c>
       <c r="E14">
-        <v>19.13293663767737</v>
+        <v>18.25344929052508</v>
       </c>
       <c r="F14">
         <v>62.61361407179756</v>
       </c>
       <c r="G14">
-        <v>18.25344929052508</v>
+        <v>19.13293663767737</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>28.86504653567735</v>
+      </c>
+      <c r="C15">
         <v>35.65149948293691</v>
-      </c>
-      <c r="C15">
-        <v>28.86504653567735</v>
       </c>
       <c r="D15">
         <v>2.804931109499637</v>
       </c>
       <c r="E15">
-        <v>21.67046436709358</v>
+        <v>17.54537597234226</v>
       </c>
       <c r="F15">
         <v>60.78415966056416</v>
       </c>
       <c r="G15">
-        <v>17.54537597234226</v>
+        <v>21.67046436709358</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>25.37808926595352</v>
+      </c>
+      <c r="C16">
         <v>45.0387310955367</v>
-      </c>
-      <c r="C16">
-        <v>25.37808926595352</v>
       </c>
       <c r="D16">
         <v>2.220311220311221</v>
       </c>
       <c r="E16">
-        <v>26.42857142857143</v>
+        <v>14.89177489177489</v>
       </c>
       <c r="F16">
         <v>58.67965367965368</v>
       </c>
       <c r="G16">
-        <v>14.89177489177489</v>
+        <v>26.42857142857143</v>
       </c>
     </row>
   </sheetData>
